--- a/public/수불자료_양식.xlsx
+++ b/public/수불자료_양식.xlsx
@@ -13,6 +13,7 @@
     <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
+    <sheet name="안내" sheetId="99" r:id="rId199"/>
     <sheet name="새제품1" sheetId="1" r:id="rId1"/>
     <sheet name="새제품2" sheetId="2" r:id="rId102"/>
     <sheet name="새제품3" sheetId="3" r:id="rId103"/>
@@ -104,7 +105,7 @@
     <t>합계</t>
   </si>
   <si>
-    <t>◀ 이 시트의 이름(아래 탭)을 제품명으로 바꿔주세요. 시트 이름이 곧 제품명입니다.</t>
+    <t>업로드 템플릿 — 월간 원재료 투입내역</t>
   </si>
   <si>
     <t>공통 재료 14개는 미리 채워져 있습니다. 수량과 단가만 입력하시면 금액과 합계는 자동으로 계산됩니다.</t>
@@ -3313,4 +3314,65 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet99.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="105" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수불자료 업로드 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.  아래 시트 탭 이름을 제품명으로 바꿔주세요.  시트 이름이 곧 제품명입니다.   (예: 새제품1 → 포기김치)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.  품명은 등록된 원재료 이름과 글자까지 같아야 합니다.  다르면 새 재료로 등록됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.  수량과 단가만 채우면 금액과 합계는 자동으로 계산됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.  쓰지 않는 시트는 지우고 올려주세요.  빈 시트는 그냥 건너뜁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.  파일 이름의 월(수불자료_26.08)과 화면에서 고른 기준 월이 같은지 확인하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">※  이 안내 시트는 업로드할 때 자동으로 무시됩니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>